--- a/data/trans_dic/P19C10_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,9</t>
+          <t>0,24; 1,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,19</t>
+          <t>0,15; 1,1</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,16</t>
+          <t>0,27; 1,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,2</t>
+          <t>0,17; 1,2</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,27</t>
+          <t>0,67; 4,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,54</t>
+          <t>0,16; 1,67</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,48</t>
+          <t>0,02; 0,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,27</t>
+          <t>0,03; 0,32</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,99</t>
+          <t>0,2; 0,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,86</t>
+          <t>0,19; 0,86</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,41</t>
+          <t>0,34; 1,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,48</t>
+          <t>0,35; 1,5</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,54</t>
+          <t>0,1; 0,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,84</t>
+          <t>0,36; 0,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,6</t>
+          <t>0,29; 0,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5696</t>
+          <t>0; 6420</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>778; 8360</t>
+          <t>1066; 8678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1712; 11152</t>
+          <t>1433; 10294</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5483</t>
+          <t>0; 6580</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>907; 8144</t>
+          <t>1027; 7343</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1519; 9922</t>
+          <t>1394; 9925</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8804</t>
+          <t>0; 9285</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1187; 8697</t>
+          <t>1105; 8016</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1347; 12692</t>
+          <t>1340; 13816</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114; 4590</t>
+          <t>161; 4523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>527; 5315</t>
+          <t>587; 6175</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6675</t>
+          <t>0; 8260</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1343; 8025</t>
+          <t>1657; 7589</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2156; 10814</t>
+          <t>2366; 10804</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8512</t>
+          <t>0; 8864</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2554; 10466</t>
+          <t>2513; 11013</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3489; 14439</t>
+          <t>3398; 14620</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3416; 17608</t>
+          <t>3404; 18031</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13003; 29403</t>
+          <t>12775; 28695</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19875; 40472</t>
+          <t>19801; 40139</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C10_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,97</t>
+          <t>0,17; 1,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,1</t>
+          <t>0,14; 1,05</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,94</t>
+          <t>0,33; 1,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,2</t>
+          <t>0,19; 1,07</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,86</t>
+          <t>0,4; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,67</t>
+          <t>0,31; 2,02</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,47</t>
+          <t>0,08; 0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,32</t>
+          <t>0,06; 0,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,93</t>
+          <t>0,25; 1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,86</t>
+          <t>0,21; 0,99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,48</t>
+          <t>0,3; 1,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,5</t>
+          <t>0,33; 1,4</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,55</t>
+          <t>0,11; 0,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,82</t>
+          <t>0,45; 0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,59</t>
+          <t>0,33; 0,65</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4493</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6420</t>
+          <t>0; 5888</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1066; 8678</t>
+          <t>833; 8886</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1433; 10294</t>
+          <t>1407; 10737</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4686</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6580</t>
+          <t>0; 5889</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1027; 7343</t>
+          <t>1360; 8181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1394; 9925</t>
+          <t>1744; 9606</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5858</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9285</t>
+          <t>0; 8272</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1105; 8016</t>
+          <t>739; 9010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1340; 13816</t>
+          <t>2008; 13080</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>955</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>3422</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3487</t>
+          <t>0; 4789</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161; 4523</t>
+          <t>681; 6615</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>587; 6175</t>
+          <t>1075; 8947</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>6078</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 8260</t>
+          <t>0; 6850</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1657; 7589</t>
+          <t>2010; 9701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2366; 10804</t>
+          <t>2753; 12873</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7401</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8864</t>
+          <t>0; 9820</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2513; 11013</t>
+          <t>2466; 10635</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3398; 14620</t>
+          <t>3430; 14596</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>31938</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3404; 18031</t>
+          <t>3677; 20191</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12775; 28695</t>
+          <t>15740; 32751</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19801; 40139</t>
+          <t>22622; 44366</t>
         </is>
       </c>
     </row>
